--- a/Reference_NMB.xlsx
+++ b/Reference_NMB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\poornima sukumar mam files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maadh\OneDrive\Desktop\PhobosQ\poornima-ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DA42A6-C9BC-49A0-A18C-2C7FBE0383DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12644025-090D-4309-8154-D7B54208DAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5CAC90CE-3BD8-4DB6-BA32-A6D0BF4ECD9E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{5CAC90CE-3BD8-4DB6-BA32-A6D0BF4ECD9E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="158">
   <si>
     <t>PostRgroupname</t>
   </si>
@@ -690,6 +690,9 @@
   </si>
   <si>
     <t>check apollo reference sheet</t>
+  </si>
+  <si>
+    <t>PostBLAge(current age)-PreRdiaage(onsetage)=duration</t>
   </si>
 </sst>
 </file>
@@ -893,9 +896,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -933,7 +936,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1039,7 +1042,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1181,7 +1184,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2086,7 +2089,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>149</v>
       </c>
@@ -2097,7 +2100,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>153</v>
       </c>
@@ -2129,7 +2132,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="101.4" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="29.4" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>141</v>
       </c>
@@ -2140,7 +2143,7 @@
         <v>135</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">

--- a/Reference_NMB.xlsx
+++ b/Reference_NMB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maadh\OneDrive\Desktop\PhobosQ\poornima-ML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/065714efc4fd34e9/Desktop/PhobosQ/poornima-ML/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12644025-090D-4309-8154-D7B54208DAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{5CAC90CE-3BD8-4DB6-BA32-A6D0BF4ECD9E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{5CAC90CE-3BD8-4DB6-BA32-A6D0BF4ECD9E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
